--- a/derivatives/BAR/P7350_preprocessed.xlsx
+++ b/derivatives/BAR/P7350_preprocessed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>listno</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>trialno</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>conceptno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>concept</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>concept_HU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>responded</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>response_HU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>similarity</t>
         </is>
@@ -845,7 +857,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.4937197268009186</v>
+        <v>0.4937196969985962</v>
       </c>
     </row>
     <row r="10">
@@ -939,7 +951,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.5492017269134521</v>
+        <v>0.5492017865180969</v>
       </c>
     </row>
     <row r="12">
@@ -1033,7 +1045,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.2204750180244446</v>
+        <v>0.2204750031232834</v>
       </c>
     </row>
     <row r="14">
@@ -1315,7 +1327,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.2988635301589966</v>
+        <v>0.298863559961319</v>
       </c>
     </row>
     <row r="20">
@@ -1733,7 +1745,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-0.0363888181746006</v>
+        <v>-0.0363888218998909</v>
       </c>
     </row>
     <row r="29">
@@ -1879,7 +1891,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.1478635668754578</v>
+        <v>0.1478635519742966</v>
       </c>
     </row>
     <row r="32">
@@ -2015,7 +2027,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.3164856135845184</v>
+        <v>0.3164855539798737</v>
       </c>
     </row>
     <row r="35">
@@ -2109,7 +2121,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.2442677915096283</v>
+        <v>0.2442678213119507</v>
       </c>
     </row>
     <row r="37">
@@ -2329,7 +2341,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.7654496431350708</v>
+        <v>0.765449583530426</v>
       </c>
     </row>
     <row r="42">
@@ -2919,7 +2931,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.5086526274681091</v>
+        <v>0.5086525678634644</v>
       </c>
     </row>
     <row r="55">
@@ -3233,7 +3245,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.820915162563324</v>
+        <v>0.8209152221679688</v>
       </c>
     </row>
     <row r="62">
@@ -3505,7 +3517,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.2316592037677765</v>
+        <v>0.2316592186689377</v>
       </c>
     </row>
     <row r="68">
@@ -3965,7 +3977,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.429463118314743</v>
+        <v>0.4294630587100983</v>
       </c>
     </row>
     <row r="78">
@@ -4069,7 +4081,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.2782971262931824</v>
+        <v>0.27829709649086</v>
       </c>
     </row>
     <row r="80">
@@ -4163,7 +4175,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.4200780689716339</v>
+        <v>0.4200780987739563</v>
       </c>
     </row>
     <row r="82">
@@ -4717,7 +4729,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.5346720218658447</v>
+        <v>0.5346719622612</v>
       </c>
     </row>
     <row r="94">
@@ -4863,7 +4875,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.6597782969474792</v>
+        <v>0.6597782373428345</v>
       </c>
     </row>
     <row r="97">
@@ -4999,7 +5011,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.6597782969474792</v>
+        <v>0.6597782373428345</v>
       </c>
     </row>
     <row r="100">
